--- a/ED-018-2026-06_Access_Options_Model_Rev_B.xlsx
+++ b/ED-018-2026-06_Access_Options_Model_Rev_B.xlsx
@@ -1453,14 +1453,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>Companion to report ED-018-2026-02 Rev B, 26 August 2026. Commercial in confidence.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" s="149" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="148" t="inlineStr">
@@ -1470,59 +1470,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="149" t="inlineStr">
         <is>
           <t>Scenarios sheet added: the marine base with and without, at current and serviced trade productivity, with live formulas.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="149" t="inlineStr">
         <is>
           <t>BaseMenu sheet added: concepts C0 to C6, each with its own cycle and availability assumption.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="149" t="inlineStr">
         <is>
           <t>Levers sheet rebuilt per option so every package reconciles from the lines above it.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="149" t="inlineStr">
         <is>
           <t>Inputs sheet extended with the written marine rate references of 24 August 2026.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="149" t="inlineStr">
         <is>
           <t>Sensitivity relabelled: the reported case is the marine review upper band; the old model base tag removed.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="149" t="inlineStr">
         <is>
           <t>Programme sheet extended with Option 1, zone phased and compressed day finish dates.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" s="149" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="149" t="inlineStr">
         <is>
           <t>Reading order: Inputs, Options, Scenarios, BaseMenu, Levers, Sensitivity, Programme, NoBase, RateCard.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="149" t="inlineStr">
         <is>
           <t>Every figure quoted in the report traces to one of these sheets.</t>
         </is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F5" s="149" t="inlineStr">
         <is>
-          <t>8 / 5 fronts; modelled finish 9 Oct 2028</t>
+          <t>8 / 5 fronts; finish 11 Oct 2028 (Option 1), 9 Oct 2028 (Option 2)</t>
         </is>
       </c>
       <c r="G5" s="149" t="inlineStr">
@@ -1864,6 +1864,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="119" t="inlineStr">
         <is>
@@ -3841,7 +3842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" style="89" min="1" max="1"/>
@@ -4079,6 +4080,49 @@
       <c r="A11" s="168" t="inlineStr">
         <is>
           <t>Basis of the serviced case: about 12 minutes each way on the roadway with passing bay waits, two crib runs and shift end, about 58 minutes per 10 hour shift; applied only to the crew paced share of the seven trade shifts (weld, blast, coat, wrap), worth about one shift per bent. Band 6.0 to 6.5 shifts; 6.0 carried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="148" t="inlineStr">
+        <is>
+          <t>OPTION 2 REFERENCES (two trade shifts per calendar day; same formula structure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>With base, serviced 6.0 trade shifts</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Finish 10 Sep 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Compressed day pattern, serviced 6.0</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Finish late Aug 2028</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5988,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="119" t="inlineStr">
         <is>
@@ -5952,7 +5995,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="175" t="inlineStr">
         <is>

--- a/ED-018-2026-06_Access_Options_Model_Rev_B.xlsx
+++ b/ED-018-2026-06_Access_Options_Model_Rev_B.xlsx
@@ -1565,7 +1565,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="175" t="inlineStr">
         <is>
@@ -1864,7 +1863,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="119" t="inlineStr">
         <is>
@@ -3994,11 +3992,11 @@
     <row r="7">
       <c r="A7" s="170" t="inlineStr">
         <is>
-          <t>With base: serviced productivity, fleet held</t>
+          <t>With base: serviced productivity, central case, fleet held</t>
         </is>
       </c>
       <c r="B7" s="170" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C7" s="170" t="n">
         <v>0.9</v>
@@ -4024,14 +4022,14 @@
       </c>
       <c r="I7" s="170" t="inlineStr">
         <is>
-          <t>Finish 5 Sep 2028; five weeks of float bought</t>
+          <t>Finish 17 Sep 2028; optimistic bound 6.0 shifts gives $14.64M, 5 Sep</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="170" t="inlineStr">
         <is>
-          <t>With base: serviced productivity, fleet trimmed</t>
+          <t>With base: serviced at the optimistic bound, fleet trimmed</t>
         </is>
       </c>
       <c r="B8" s="170" t="n">
@@ -4091,36 +4089,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="149" t="inlineStr">
         <is>
           <t>With base, serviced 6.0 trade shifts</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="149" t="n">
         <v>5</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="149" t="n">
         <v>13.25</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="149" t="inlineStr">
         <is>
           <t>Finish 10 Sep 2028</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="149" t="inlineStr">
         <is>
           <t>Compressed day pattern, serviced 6.0</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="149" t="n">
         <v>6</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="149" t="n">
         <v>12.92</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="149" t="inlineStr">
         <is>
           <t>Finish late Aug 2028</t>
         </is>
